--- a/public/templates/Shablloni-2-Faqe.xlsx
+++ b/public/templates/Shablloni-2-Faqe.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Graniti\Junik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\AAB\Viti 3 Semestri 6\Tema-Graniti\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A740A52-96B7-4C0C-967A-DCEAD0974589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D255423E-EA37-4023-9D8C-B45344B28E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -610,6 +610,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -655,32 +667,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1005,11 +1005,11 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="51"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="55"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -1024,35 +1024,35 @@
         <v>7</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="66" t="s">
+      <c r="F3" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="67"/>
-      <c r="H3" s="68"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="73"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="C4" s="1"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="68"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="73"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="68"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="73"/>
     </row>
     <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="47" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="68"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="73"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
@@ -1078,13 +1078,13 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="65"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="70"/>
       <c r="F9" s="16" t="s">
         <v>6</v>
       </c>
@@ -1094,21 +1094,21 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="64"/>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="65"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="70"/>
       <c r="F10" s="5"/>
       <c r="G10" s="6"/>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="64"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="65"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="70"/>
       <c r="F11" s="5" t="s">
         <v>24</v>
       </c>
@@ -1118,11 +1118,11 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="69"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="71"/>
+      <c r="A12" s="50"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="52"/>
       <c r="F12" s="17"/>
       <c r="G12" s="18"/>
       <c r="H12" s="48"/>
@@ -1135,11 +1135,11 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="55" t="s">
+      <c r="F13" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="56"/>
-      <c r="H13" s="57"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="61"/>
     </row>
     <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
@@ -1151,9 +1151,9 @@
       <c r="E14" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="58"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="60"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="64"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -1186,33 +1186,33 @@
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="54"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="58"/>
       <c r="F17" s="5"/>
       <c r="G17" s="6"/>
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="52"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54"/>
+      <c r="A18" s="56"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="58"/>
       <c r="F18" s="5"/>
       <c r="G18" s="6"/>
       <c r="H18" s="12"/>
     </row>
     <row r="19" spans="1:8" ht="100.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="52"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54"/>
+      <c r="A19" s="56"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="58"/>
       <c r="F19" s="5"/>
       <c r="G19" s="6"/>
       <c r="H19" s="12"/>
@@ -1225,7 +1225,7 @@
       <c r="E20" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="73">
+      <c r="F20" s="53">
         <v>1</v>
       </c>
       <c r="G20" s="35"/>
@@ -1267,23 +1267,23 @@
       <c r="H23" s="42"/>
     </row>
     <row r="24" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="61" t="s">
+      <c r="A24" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="63"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="67"/>
       <c r="F24" s="40"/>
       <c r="G24" s="41"/>
       <c r="H24" s="42"/>
     </row>
     <row r="25" spans="1:8" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="61"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
+      <c r="A25" s="65"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
       <c r="F25" s="40"/>
       <c r="G25" s="41"/>
       <c r="H25" s="42"/>
@@ -1296,7 +1296,7 @@
       <c r="E26" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="73">
+      <c r="F26" s="53">
         <v>1</v>
       </c>
       <c r="G26" s="49"/>
@@ -1328,21 +1328,21 @@
       <c r="H28" s="41"/>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="61"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="63"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="67"/>
       <c r="F29" s="40"/>
       <c r="G29" s="41"/>
       <c r="H29" s="42"/>
     </row>
     <row r="30" spans="1:8" ht="12.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="61"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="62"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="63"/>
+      <c r="A30" s="65"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="67"/>
       <c r="F30" s="40"/>
       <c r="G30" s="41"/>
       <c r="H30" s="42"/>

--- a/public/templates/Shablloni-2-Faqe.xlsx
+++ b/public/templates/Shablloni-2-Faqe.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\AAB\Viti 3 Semestri 6\Tema-Graniti\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D255423E-EA37-4023-9D8C-B45344B28E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FCC042-949A-410C-BB04-DC03C0043AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -527,7 +527,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -582,9 +582,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
@@ -595,16 +592,6 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -665,6 +652,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -672,15 +668,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -988,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" customWidth="1"/>
@@ -1005,11 +992,11 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="54"/>
-      <c r="H1" s="55"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -1024,35 +1011,35 @@
         <v>7</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="72"/>
-      <c r="H3" s="73"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="C4" s="1"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="73"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="65"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="73"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="65"/>
     </row>
     <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="42" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="73"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="65"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
@@ -1078,13 +1065,13 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="70"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="68"/>
       <c r="F9" s="16" t="s">
         <v>6</v>
       </c>
@@ -1094,21 +1081,21 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="68"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="70"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="68"/>
       <c r="F10" s="5"/>
       <c r="G10" s="6"/>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="70"/>
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="68"/>
       <c r="F11" s="5" t="s">
         <v>24</v>
       </c>
@@ -1118,14 +1105,14 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="50"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="52"/>
+      <c r="A12" s="45"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="47"/>
       <c r="F12" s="17"/>
       <c r="G12" s="18"/>
-      <c r="H12" s="48"/>
+      <c r="H12" s="43"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -1135,11 +1122,11 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="59" t="s">
+      <c r="F13" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="60"/>
-      <c r="H13" s="61"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="56"/>
     </row>
     <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
@@ -1151,9 +1138,9 @@
       <c r="E14" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="62"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="64"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="59"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -1186,33 +1173,33 @@
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="58"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="53"/>
       <c r="F17" s="5"/>
       <c r="G17" s="6"/>
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="56"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="58"/>
+      <c r="A18" s="51"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="53"/>
       <c r="F18" s="5"/>
       <c r="G18" s="6"/>
       <c r="H18" s="12"/>
     </row>
-    <row r="19" spans="1:8" ht="100.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="56"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="58"/>
+    <row r="19" spans="1:8" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="51"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="53"/>
       <c r="F19" s="5"/>
       <c r="G19" s="6"/>
       <c r="H19" s="12"/>
@@ -1225,11 +1212,11 @@
       <c r="E20" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="48">
         <v>1</v>
       </c>
-      <c r="G20" s="35"/>
-      <c r="H20" s="36"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="35"/>
     </row>
     <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="22"/>
@@ -1239,9 +1226,9 @@
       <c r="E21" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="37"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39">
+      <c r="F21" s="36"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="38">
         <f>F20</f>
         <v>1</v>
       </c>
@@ -1252,9 +1239,9 @@
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
       <c r="E22" s="24"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="42"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:8" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="29"/>
@@ -1262,31 +1249,31 @@
       <c r="C23" s="30"/>
       <c r="D23" s="30"/>
       <c r="E23" s="31"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="42"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="24" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="65" t="s">
+      <c r="A24" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="66"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="42"/>
-    </row>
-    <row r="25" spans="1:8" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="65"/>
-      <c r="B25" s="66"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="42"/>
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="41"/>
+    </row>
+    <row r="25" spans="1:8" ht="168.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="60"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
     </row>
     <row r="26" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="29"/>
@@ -1296,11 +1283,11 @@
       <c r="E26" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="53">
+      <c r="F26" s="48">
         <v>1</v>
       </c>
-      <c r="G26" s="49"/>
-      <c r="H26" s="36"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="35"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="29"/>
@@ -1310,188 +1297,93 @@
       <c r="E27" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39">
+      <c r="F27" s="36"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38">
         <f>F26</f>
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="29"/>
       <c r="B28" s="30"/>
       <c r="C28" s="30"/>
       <c r="D28" s="30"/>
       <c r="E28" s="31"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-    </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="65"/>
-      <c r="B29" s="66"/>
-      <c r="C29" s="66"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="42"/>
-    </row>
-    <row r="30" spans="1:8" ht="12.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="65"/>
-      <c r="B30" s="66"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="42"/>
-    </row>
-    <row r="31" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="29"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="36"/>
-    </row>
-    <row r="32" spans="1:8" ht="8.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="45"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="44"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="22"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="36"/>
-    </row>
-    <row r="34" spans="1:8" ht="1.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="45"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="42"/>
-    </row>
-    <row r="35" spans="1:8" ht="8.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="45"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="44"/>
-    </row>
-    <row r="36" spans="1:8" ht="4.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="12"/>
-    </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="12"/>
-    </row>
-    <row r="38" spans="1:8" ht="9.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="12"/>
-    </row>
-    <row r="39" spans="1:8" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="12"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="33"/>
-    </row>
-    <row r="41" spans="1:8" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="5"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="21"/>
-    </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="22"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="21"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="5"/>
-      <c r="E43" s="6" t="s">
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="33"/>
+    </row>
+    <row r="30" spans="1:8" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="21"/>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="22"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="21"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+      <c r="E32" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F43" s="5"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="12"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="5"/>
-      <c r="E44" s="6" t="s">
+      <c r="F32" s="5"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="12"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="E33" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F44" s="5"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="12"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="7"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="9" t="s">
+      <c r="F33" s="5"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="12"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="7"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F45" s="7"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="14"/>
-    </row>
-    <row r="47" spans="1:8" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="F34" s="7"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="14"/>
+    </row>
+    <row r="36" spans="1:8" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>17</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F36" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="25.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:8" ht="25.2" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A17:E19"/>
     <mergeCell ref="F13:H14"/>
     <mergeCell ref="A24:E25"/>
-    <mergeCell ref="A29:E30"/>
     <mergeCell ref="F3:H6"/>
     <mergeCell ref="A9:E11"/>
   </mergeCells>
